--- a/plantillas/47.xlsx
+++ b/plantillas/47.xlsx
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/47.xlsx
+++ b/plantillas/47.xlsx
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/47.xlsx
+++ b/plantillas/47.xlsx
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
     </row>
